--- a/docs/assets/bestanden/MutatieAreaaldata43D4_50D1.xlsx
+++ b/docs/assets/bestanden/MutatieAreaaldata43D4_50D1.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provincienoordholland-my.sharepoint.com/personal/burenm_noord-holland_nl/Documents/Documenten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provincienoordholland.sharepoint.com/teams/bu-bms/Documentensets/Objectdefinities en Attributenlijsten AD5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{6EBBF117-A2A8-43DA-8717-B6FA591404EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B4554BD-4DD3-4813-B198-FBFDA2D3CAD1}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1F7CB4E0-25F6-40C4-82C5-9A18C0429E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{445A4FCD-00BE-4A1A-B6B0-66FA5356E661}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{FA75E84B-D7F2-415F-BFF1-996E100EF30F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataflow" sheetId="1" r:id="rId1"/>
-    <sheet name="DefQuerie" sheetId="2" r:id="rId2"/>
+    <sheet name="DefQuery" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,22 +36,1585 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>dummy, wordt nog gevuld</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="520">
+  <si>
+    <t>AD4 Feature Class</t>
+  </si>
+  <si>
+    <t>AD5 Feature Class</t>
+  </si>
+  <si>
+    <t>Definition Statement</t>
+  </si>
+  <si>
+    <t>AREAALDATA.adres_tbl</t>
+  </si>
+  <si>
+    <t>adres_tbl</t>
+  </si>
+  <si>
+    <t>(x in x)</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bak_p</t>
+  </si>
+  <si>
+    <t>afvalbak_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:afvalbak','niet-bgt:afval apart plaats'))</t>
+  </si>
+  <si>
+    <t>opslagbak_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:zand- / zoutbak'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeelBermKr_l</t>
+  </si>
+  <si>
+    <t>profiellijn_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeelBerm_v</t>
+  </si>
+  <si>
+    <t>duin_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('duin','duin:gesloten duinvegetatie','duin:open duinvegetatie'))</t>
+  </si>
+  <si>
+    <t>gras_en_kruidachtigen_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('grasland agrarisch','grasland overig','groenvoorziening:gras- en kruidachtigen'))</t>
+  </si>
+  <si>
+    <t>groenobject_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeelKruin_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeelPlKr_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeelPlantvak_v</t>
+  </si>
+  <si>
+    <t>bos_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gemengd bos','loofbos','loofbos:griend en hakhout','naaldbos'))</t>
+  </si>
+  <si>
+    <t>bosplantsoen_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening:bosplantsoen'))</t>
+  </si>
+  <si>
+    <t>heide_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('heide'))</t>
+  </si>
+  <si>
+    <t>planten_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening:planten'))</t>
+  </si>
+  <si>
+    <t>rietland_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('rietland'))</t>
+  </si>
+  <si>
+    <t>struiken_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening:bodembedekkers','groenvoorziening:heesters','groenvoorziening:struikrozen','struiken'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.begroeidTerreindeel_v</t>
+  </si>
+  <si>
+    <t>bouwland_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('bouwland','bouwland:bollenteelt','bouwland:akkerbouw','bouwland:vollegrondsteelt','bouwland:braakliggend'))</t>
+  </si>
+  <si>
+    <t>fruit_of_kweekbomen_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('fruitteelt','boomteelt','fruitteelt:hoogstam boomgaarden','fruitteelt:laagstam boomgaarden','fruitteelt:wijngaarden','fruitteelt:klein fruit'))</t>
+  </si>
+  <si>
+    <t>houtwal_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('houtwal'))</t>
+  </si>
+  <si>
+    <t>moeras_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('moeras'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.beheergrenzen_v</t>
+  </si>
+  <si>
+    <t>beheervak_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bordDRIS_p</t>
+  </si>
+  <si>
+    <t>informatiepaneel_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bordScheepvaart_p</t>
+  </si>
+  <si>
+    <t>informatiebord_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Informatiebord'))</t>
+  </si>
+  <si>
+    <t>kabels_en_leidingenbord_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('bord kabels/leidingen'))</t>
+  </si>
+  <si>
+    <t>scheepvaartbord_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('BPR bord','Route verwijsbord'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bordZwemwater_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bord_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:informatiebord'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:dynamische snelheidsindicator'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:verklikker transportleiding'))</t>
+  </si>
+  <si>
+    <t>reclamebord_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:reclamebord'))</t>
+  </si>
+  <si>
+    <t>verkeersbord_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:plaatsnaambord','niet-bgt:straatnaambord','niet-bgt:verkeersbord','niet-bgt:waarschuwingshek','niet-bgt:wegwijzer','niet-bgt'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bouwdeelGeluidsscherm_tbl</t>
+  </si>
+  <si>
+    <t>kunstwerkbouwdeel_tbl</t>
+  </si>
+  <si>
+    <t>neninspectie_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bouwdeelKunstwerk_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.bouwdeelOevervak_tbl</t>
+  </si>
+  <si>
+    <t>oeverbouwdeel_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.buis_l</t>
+  </si>
+  <si>
+    <t>aansluitleiding_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('aansluitleiding'))</t>
+  </si>
+  <si>
+    <t>drain_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('drainagebuis'))</t>
+  </si>
+  <si>
+    <t>vrijvervalrioolleiding_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('hemelwaterriool','overstortleiding','stuwrioolleiding', 'vuilwaterriool','doorlatendeleiding','zinker','transportrioolleiding'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.crowInspectie_tbl</t>
+  </si>
+  <si>
+    <t>crowinspectie_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.crowInspectieresultaat_tbl</t>
+  </si>
+  <si>
+    <t>crowinspectieresultaat_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.crowMeting_tbl</t>
+  </si>
+  <si>
+    <t>crowmeting_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.ecopassage_l</t>
+  </si>
+  <si>
+    <t>faunameubilair_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Loopplank onder brug'))</t>
+  </si>
+  <si>
+    <t>faunaverblijfplaats_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Vleermuisbunker'))</t>
+  </si>
+  <si>
+    <t>faunavoorziening_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Amfibieëntunnel','Boombrug','brug of viaduct met faunavoorziening','Duiker, Looprichel','ecoduiker / duiker met faunavoorziening','kleine faunatunnel','Looprichel','Onduidelijk','Overig','Overige faunatunnel','tunnel / viaduct met medegebruik fauna'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.elektriciteitskabel_l</t>
+  </si>
+  <si>
+    <t>combikabel_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('ADD'))</t>
+  </si>
+  <si>
+    <t>datakabel_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('DAT'))</t>
+  </si>
+  <si>
+    <t>voedingskabel_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('ENE'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.elementOevervak_tbl</t>
+  </si>
+  <si>
+    <t>oeverelement_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.faunavoorziening_v</t>
+  </si>
+  <si>
+    <t>gebied_faunavoorziening_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.fietsparkeervoorziening_l</t>
+  </si>
+  <si>
+    <t>fietsparkeervoorziening_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.functioneelGebied_v</t>
+  </si>
+  <si>
+    <t>werkgebied_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.gebiedscontractregio_v</t>
+  </si>
+  <si>
+    <t>beheergebied_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.gebouwInstallatie_v</t>
+  </si>
+  <si>
+    <t>bordes_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:bordes'))</t>
+  </si>
+  <si>
+    <t>luifel_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:luifel'))</t>
+  </si>
+  <si>
+    <t>toegangstrap_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:toegangstrap'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.geluidwerendeVoorziening_l</t>
+  </si>
+  <si>
+    <t>geluidwerendeconstructie_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.halte_v</t>
+  </si>
+  <si>
+    <t>halteplaats_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.installatie_p</t>
+  </si>
+  <si>
+    <t>pomp_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:pomp'))</t>
+  </si>
+  <si>
+    <t>zonnepaneel_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:zonnepaneel'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kastDRIS_p</t>
+  </si>
+  <si>
+    <t>telecomkast_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kastOvl_p</t>
+  </si>
+  <si>
+    <t>ovl_kast_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kastVri_p</t>
+  </si>
+  <si>
+    <t>vri_kast_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kast_p</t>
+  </si>
+  <si>
+    <t>besturingskast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Rioolpompkast'))</t>
+  </si>
+  <si>
+    <t>cai_kast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('CAI'))</t>
+  </si>
+  <si>
+    <t>elektriciteitskast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Elec'))</t>
+  </si>
+  <si>
+    <t>gaskast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Gaskast'))</t>
+  </si>
+  <si>
+    <t>gms_kast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('GMS-kast'))</t>
+  </si>
+  <si>
+    <t>kast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Kast: onbekend','OV'))</t>
+  </si>
+  <si>
+    <t>slagboominstallatie_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Slagboomkast'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Schakelkast PTT'))</t>
+  </si>
+  <si>
+    <t>telkast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Telkast: onbekend'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kleineHalteDisplay_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kruispunt_p</t>
+  </si>
+  <si>
+    <t>kruispunt_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kunstwerk_p</t>
+  </si>
+  <si>
+    <t>aquaduct_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Aquaducten'))</t>
+  </si>
+  <si>
+    <t>beweegbarebrug_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Bruggen (beweegbaar)'))</t>
+  </si>
+  <si>
+    <t>duiker_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Duikers','Overkluizingen','Sifons'))</t>
+  </si>
+  <si>
+    <t>ecoduct_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Ecoducten'))</t>
+  </si>
+  <si>
+    <t>flyover_p</t>
+  </si>
+  <si>
+    <t>(BEHEEROBJECTSUBTYP in ('Fly-over'))</t>
+  </si>
+  <si>
+    <t>gemaalcomplex_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Gemalen'))</t>
+  </si>
+  <si>
+    <t>onderdoorgang_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Onderdoorgangen'))</t>
+  </si>
+  <si>
+    <t>overigkunstwerk_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Spoorwegen','Grondkeringen','Faunatunnel','Onbekend','Wateren en watergangen (niet lijnvormig), overig'))</t>
+  </si>
+  <si>
+    <t>sluiscomplex_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Schutsluizen'))</t>
+  </si>
+  <si>
+    <t>tunnel_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Tunnels'))</t>
+  </si>
+  <si>
+    <t>vastebrug_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Bruggen (vast)'))</t>
+  </si>
+  <si>
+    <t>veerverbinding_p</t>
+  </si>
+  <si>
+    <t>(NENBEHEEROBJECT in ('Recreatieve gebieden'))</t>
+  </si>
+  <si>
+    <t>viaduct_p</t>
+  </si>
+  <si>
+    <t>(BEHEEROBJECTSUBTYP in ('HA','VD'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kunstwerkdeel_l</t>
+  </si>
+  <si>
+    <t>duiker_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt', 'niet-bgt:duiker'))</t>
+  </si>
+  <si>
+    <t>kunstwerkdeel_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt'))</t>
+  </si>
+  <si>
+    <t>stuw_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('stuw'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kunstwerkdeel_mp</t>
+  </si>
+  <si>
+    <t>hoogspanningsmast_mp</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('hoogspanningsmast'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kunstwerkdeel_v</t>
+  </si>
+  <si>
+    <t>coupure_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:coupure'))</t>
+  </si>
+  <si>
+    <t>duiker_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:duiker'))</t>
+  </si>
+  <si>
+    <t>faunavoorziening_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:faunavoorziening','niet-bgt:vispassage'))</t>
+  </si>
+  <si>
+    <t>folie_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt')) and (TYPESPEC in ('Folie'))</t>
+  </si>
+  <si>
+    <t>gemaal_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('gemaal'))</t>
+  </si>
+  <si>
+    <t>hoogspanningsmast_v</t>
+  </si>
+  <si>
+    <t>kunstwerkdeel_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Overig')) and (BGTPLUSTYPE in ('niet-bgt'))</t>
+  </si>
+  <si>
+    <t>kwelscherm_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt')) and (TYPESPEC in ('Kwelscherm'))</t>
+  </si>
+  <si>
+    <t>muur_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:keermuur')) and (RELATIEVEHOOGTELIGGING in ('0','1','2'))</t>
+  </si>
+  <si>
+    <t>perron_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('perron'))</t>
+  </si>
+  <si>
+    <t>ponton_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:ponton'))</t>
+  </si>
+  <si>
+    <t>sluisdeur_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('sluis'))</t>
+  </si>
+  <si>
+    <t>steiger_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('steiger'))</t>
+  </si>
+  <si>
+    <t>stuw_v</t>
+  </si>
+  <si>
+    <t>tunnelwand_v</t>
+  </si>
+  <si>
+    <t>(RELATIEVEHOOGTELIGGING in ('-1')) and (BGTPLUSTYPE in ('niet-bgt:keermuur'))</t>
+  </si>
+  <si>
+    <t>voorde_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:voorde'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.kwElement_tbl</t>
+  </si>
+  <si>
+    <t>kunstwerkelement_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.lamp_p</t>
+  </si>
+  <si>
+    <t>lichtbron_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.lantaarn_p</t>
+  </si>
+  <si>
+    <t>verkeerslantaarn_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.leidingelement_p</t>
+  </si>
+  <si>
+    <t>aansluitput_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Zandvang'))</t>
+  </si>
+  <si>
+    <t>aardelektrode_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('aarding'))</t>
+  </si>
+  <si>
+    <t>drainageput_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Drainageput'))</t>
+  </si>
+  <si>
+    <t>kolk_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Kolk','RWS kolk','Straatkolk','Trottoirkolk','Rioolleidingelement: onbekend'))</t>
+  </si>
+  <si>
+    <t>rioolafsluiter_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('cleanOut'))</t>
+  </si>
+  <si>
+    <t>rioolput_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Inspectieput'))</t>
+  </si>
+  <si>
+    <t>verbindingsstuk_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('DEM','mof'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.ligplaatsstrook_v</t>
+  </si>
+  <si>
+    <t>ligplaatsstrook_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.mantelbuis_v</t>
+  </si>
+  <si>
+    <t>mantelbuis_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.mast_p</t>
+  </si>
+  <si>
+    <t>paal_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:laagspanningsmast'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.oevervak_v</t>
+  </si>
+  <si>
+    <t>oeverzone_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.onbegroeidTerreindeelKruin_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.onbegroeidTerreindeel_v</t>
+  </si>
+  <si>
+    <t>asfaltverharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gesloten verharding:asfalt'))</t>
+  </si>
+  <si>
+    <t>betonverharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gesloten verharding:cementbeton'))</t>
+  </si>
+  <si>
+    <t>elementenverharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('open verharding','open verharding:beton element','open verharding:betonstraatstenen','open verharding:gebakken klinkers','open verharding:sierbestrating','open verharding:tegels','half verhard:grasklinkers'))</t>
+  </si>
+  <si>
+    <t>halfverharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('half verhard','half verhard:gravel','half verhard:grind','half verhard:puin','half verhard:schelpen'))</t>
+  </si>
+  <si>
+    <t>kunststofverharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gesloten verharding:kunststof'))</t>
+  </si>
+  <si>
+    <t>onverhard_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('onverhard','onverhard:boomschors','onverhard:zand'))</t>
+  </si>
+  <si>
+    <t>verharding_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gesloten verharding','Erf'))</t>
+  </si>
+  <si>
+    <t>zandvlakte_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('zand','zand:zandverstuiving','zand:strand en strandwal'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.ondersteunendWaterdeel_v</t>
+  </si>
+  <si>
+    <t>getijdengebied_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('slik'))</t>
+  </si>
+  <si>
+    <t>oever_of_slootkant_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.ondersteunendWegdeelKruin_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.ondersteunendWegdeel_v</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening:gras- en kruidachtigen'))</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('groenvoorziening:bodembedekkers','groenvoorziening:heesters','groenvoorziening:struikrozen'))</t>
+  </si>
+  <si>
+    <t>(FYSIEKVOORKOMEN in ('gesloten verharding'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.overbruggingsdeel_v</t>
+  </si>
+  <si>
+    <t>dek_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('dek'))</t>
+  </si>
+  <si>
+    <t>landhoofd_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('landhoofd'))</t>
+  </si>
+  <si>
+    <t>overbruggingsdeel_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('Null'))</t>
+  </si>
+  <si>
+    <t>pijler_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('pijler'))</t>
+  </si>
+  <si>
+    <t>pyloon_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('pyloon'))</t>
+  </si>
+  <si>
+    <t>sloof_v</t>
+  </si>
+  <si>
+    <t>(TYPEOVERBRUGGINGSDEEL in ('sloof'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.overigBouwwerk_v</t>
+  </si>
+  <si>
+    <t>bergbezinkbassin_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('bezinkbak'))</t>
+  </si>
+  <si>
+    <t>dok_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('bassin'))</t>
+  </si>
+  <si>
+    <t>gebouw_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:bunker','niet-bgt:schuur','lage trafo'))</t>
+  </si>
+  <si>
+    <t>open_loods_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('open loods'))</t>
+  </si>
+  <si>
+    <t>opslagtank_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('opslagtank'))</t>
+  </si>
+  <si>
+    <t>overigbouwwerk_v</t>
+  </si>
+  <si>
+    <t>overkapping_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('overkapping'))</t>
+  </si>
+  <si>
+    <t>windturbine_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('windturbine'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.paalAfbakening_p</t>
+  </si>
+  <si>
+    <t>afsluitpaal_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Afsluiter','schamppaal'))</t>
+  </si>
+  <si>
+    <t>markeringspaal_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('dijkpaal','grensmarkering'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Paal'))</t>
+  </si>
+  <si>
+    <t>poller_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Poller'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('hectometerbord_scheepvaart'))</t>
+  </si>
+  <si>
+    <t>telpaal_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Telpaal'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Hectometerpaal','Bermplank'))</t>
+  </si>
+  <si>
+    <t>vlaggenmast_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Vlaggenmast'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.paalDraagconstructie_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:afsluitpaal'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:dijkpaal'))</t>
+  </si>
+  <si>
+    <t>meldpaal_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:drukknoppaal','niet-bgt:praatpaal'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:haltepaal','niet-bgt:lichtmast','niet-bgt:verkeersbordpaal','niet-bgt:verkeersregelinstallatiepaal','niet-bgt:portaal','niet-bgt'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:poller'))</t>
+  </si>
+  <si>
+    <t>sirene_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:sirene'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:vlaggenmast'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.pand_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.peilbuis_p</t>
+  </si>
+  <si>
+    <t>peilbuis_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.perron_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.plaaginvasiesoortInspectie_p</t>
+  </si>
+  <si>
+    <t>plantensoortlocatie_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.put_p</t>
+  </si>
+  <si>
+    <t>brandkraan_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:brandkraan / -put'))</t>
+  </si>
+  <si>
+    <t>gasput_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:gasput'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:kolk'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:inspectie- / rioolput'))</t>
+  </si>
+  <si>
+    <t>waterleidingput_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:waterleidingput'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.scheidingGeleidewand_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.scheidingGeluidsscherm_l</t>
+  </si>
+  <si>
+    <t>geluidsscherm_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.scheidingLand_l</t>
+  </si>
+  <si>
+    <t>hek_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('hek','niet-bgt:draadraster','niet-bgt'))</t>
+  </si>
+  <si>
+    <t>muur_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('muur'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.scheidingWater_l</t>
+  </si>
+  <si>
+    <t>beschoeiing_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('walbescherming'))</t>
+  </si>
+  <si>
+    <t>damwand_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('damwand'))</t>
+  </si>
+  <si>
+    <t>kademuur_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('kademuur'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.scheiding_v</t>
+  </si>
+  <si>
+    <t>kademuur_v</t>
+  </si>
+  <si>
+    <t>(RELATIEVEHOOGTELIGGING in ('0','1','2')) and (BGTPLUSTYPE in ('muur'))</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('muur')) and (RELATIEVEHOOGTELIGGING in ('-1'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.sensor_l</t>
+  </si>
+  <si>
+    <t>detector_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.sensor_p</t>
+  </si>
+  <si>
+    <t>antenne_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Kar antenne'))</t>
+  </si>
+  <si>
+    <t>camera_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Detectie: camera overig','ObservatieCamera','Straatmeubilair: camera'))</t>
+  </si>
+  <si>
+    <t>detector_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Radar detector'))</t>
+  </si>
+  <si>
+    <t>drukknop_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Drukknopsensor'))</t>
+  </si>
+  <si>
+    <t>gms_sensor_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('GMS-sensor geleiding','GMS-sensor temperatuur'))</t>
+  </si>
+  <si>
+    <t>handhavingssysteem_p</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:flitser')) and (TYPESPEC in ('Detectie: flitspaal'))</t>
+  </si>
+  <si>
+    <t>lichtsensor_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Schemerschakelaar'))</t>
+  </si>
+  <si>
+    <t>rateltikker_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Rateltikker'))</t>
+  </si>
+  <si>
+    <t>weerstation_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Weerstation'))</t>
+  </si>
+  <si>
+    <t>windmeter_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Windmeter'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.straatmeubilairAbri_p</t>
+  </si>
+  <si>
+    <t>abri_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.straatmeubilairLichtpunt_p</t>
+  </si>
+  <si>
+    <t>actievewegmarkering_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('AM'))</t>
+  </si>
+  <si>
+    <t>armatuur_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('MU','ARM'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.straatmeubilair_p</t>
+  </si>
+  <si>
+    <t>akoestische_signaalgever_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('bel'))</t>
+  </si>
+  <si>
+    <t>betaalautomaat_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Betaalautomaat'))</t>
+  </si>
+  <si>
+    <t>bolder_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Bolder'))</t>
+  </si>
+  <si>
+    <t>brievenbus_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Brievenbus'))</t>
+  </si>
+  <si>
+    <t>fietsparkeervoorziening_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('fietsenrek'))</t>
+  </si>
+  <si>
+    <t>fontein_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Fontein'))</t>
+  </si>
+  <si>
+    <t>herdenkingsmonument_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Herdenkingsmonument'))</t>
+  </si>
+  <si>
+    <t>hijsinrichting_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Bootkraan prive'))</t>
+  </si>
+  <si>
+    <t>kunstobject_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('kunstobject'))</t>
+  </si>
+  <si>
+    <t>luidspreker_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Luidspreker'))</t>
+  </si>
+  <si>
+    <t>rookpaal_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Peukenpaal'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Slagboom'))</t>
+  </si>
+  <si>
+    <t>tafel_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Picknick tafel'))</t>
+  </si>
+  <si>
+    <t>veiligheidsvoorziening_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Lier','Nooduitgangtrap','Reddingsboei','Inspringvoorziening'))</t>
+  </si>
+  <si>
+    <t>verkeersspiegel_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('verkeersspiegel'))</t>
+  </si>
+  <si>
+    <t>wegdekreflector_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Reflector'))</t>
+  </si>
+  <si>
+    <t>zitelement_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('zitbank'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.telecommunicatiekabel_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.theorHectometrering_p</t>
+  </si>
+  <si>
+    <t>theoretische_hectometrering_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.traject_v</t>
+  </si>
+  <si>
+    <t>weg_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Busbaan','Fietspad','Weg'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.tunneldeel_v</t>
+  </si>
+  <si>
+    <t>tunnelbuis_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.uitleggerPortaal_l</t>
+  </si>
+  <si>
+    <t>portaal_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Portaal'))</t>
+  </si>
+  <si>
+    <t>zweepmast_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Uitlegger'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.utiliteitsNet_tbl</t>
+  </si>
+  <si>
+    <t>utiliteitsnet_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vaarweg_l</t>
+  </si>
+  <si>
+    <t>vaarwegas_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vaarwegdeeltraject_v</t>
+  </si>
+  <si>
+    <t>vaarweg_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vaarwegdeeltrajectas_l</t>
+  </si>
+  <si>
+    <t>vaarwegdeeltrajectas_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vegetatieObject_l</t>
+  </si>
+  <si>
+    <t>haag_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:haag'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vegetatieObject_p</t>
+  </si>
+  <si>
+    <t>boom_p</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vegetatieObject_v</t>
+  </si>
+  <si>
+    <t>boomspiegel_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Boomspiegel'))</t>
+  </si>
+  <si>
+    <t>groeiplaats_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Groeiplaatsinrichting'))</t>
+  </si>
+  <si>
+    <t>haag_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Haag'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.vtaInspectie_tbl</t>
+  </si>
+  <si>
+    <t>bvc_inspectie_tbl</t>
+  </si>
+  <si>
+    <t>AREAALDATA.waterdeel_v</t>
+  </si>
+  <si>
+    <t>watergang_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('greppel, droge sloot','waterloop','waterloop:sloot','waterloop:kanaal','waterloop:rivier','waterloop:gracht'))</t>
+  </si>
+  <si>
+    <t>watervlakte_v</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('watervlakte','watervlakte:haven','watervlakte:meer, plas, ven, vijver','zee'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.waterinrichtingselement_l</t>
+  </si>
+  <si>
+    <t>geleidewerk_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:geleidewerk'))</t>
+  </si>
+  <si>
+    <t>remmingswerk_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:remmingswerk'))</t>
+  </si>
+  <si>
+    <t>vuilvang_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:vuilvang'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.waterinrichtingselement_p</t>
+  </si>
+  <si>
+    <t>betonning_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Baken'))</t>
+  </si>
+  <si>
+    <t>hoogtemerk_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Hoogtemerk'))</t>
+  </si>
+  <si>
+    <t>meerpaal_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Dukdalf','Meerpaal'))</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Drenkelingenladder'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.waterloop_l</t>
+  </si>
+  <si>
+    <t>watergang_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.weg_l</t>
+  </si>
+  <si>
+    <t>wegas_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.wegdeelKruin_l</t>
+  </si>
+  <si>
+    <t>AREAALDATA.wegdeel_v</t>
+  </si>
+  <si>
+    <t>AREAALDATA.weginrichtingselement_l</t>
+  </si>
+  <si>
+    <t>balustrade_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:balustrade'))</t>
+  </si>
+  <si>
+    <t>band_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('OPS'))</t>
+  </si>
+  <si>
+    <t>geleideconstructie_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('GR','VC','MSB'))</t>
+  </si>
+  <si>
+    <t>lijngoot_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Lijnafwatering'))</t>
+  </si>
+  <si>
+    <t>molgoot_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Molgoot'))</t>
+  </si>
+  <si>
+    <t>rijstrookscheiding_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('VRBS'))</t>
+  </si>
+  <si>
+    <t>verblindingswering_l</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:verblindingswering'))</t>
+  </si>
+  <si>
+    <t>voegovergang_l</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Voegovergang') )</t>
+  </si>
+  <si>
+    <t>wegmarkering_tbl</t>
+  </si>
+  <si>
+    <t>(BGTPLUSTYPE in ('niet-bgt:wegmarkering'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.weginrichtingselement_p</t>
+  </si>
+  <si>
+    <t>blok_p</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('schampblok'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.weginrichtingselement_v</t>
+  </si>
+  <si>
+    <t>geleideconstructie_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Barrier'))</t>
+  </si>
+  <si>
+    <t>rooster_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Wildrooster','Rooster'))</t>
+  </si>
+  <si>
+    <t>verkeersdrempel_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Verkeersdrempel'))</t>
+  </si>
+  <si>
+    <t>zonnepaneel_v</t>
+  </si>
+  <si>
+    <t>(TYPESPEC in ('Zonnefietspad'))</t>
+  </si>
+  <si>
+    <t>AREAALDATA.wegvak_v</t>
+  </si>
+  <si>
+    <t>wegvak_v</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,8 +1637,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -410,25 +1973,3128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C397F3D-BAD7-4A2D-9E8D-F493166F97E3}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42819821-0C53-4A2C-8873-DB33CC2A5C79}">
+  <dimension ref="A1:C283"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="36.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
+        <v>121</v>
+      </c>
+      <c r="C63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>129</v>
+      </c>
+      <c r="B67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>129</v>
+      </c>
+      <c r="B73" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C74" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>147</v>
+      </c>
+      <c r="B76" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" t="s">
+        <v>151</v>
+      </c>
+      <c r="C78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>155</v>
+      </c>
+      <c r="C80" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B83" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B84" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" t="s">
+        <v>163</v>
+      </c>
+      <c r="C85" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>150</v>
+      </c>
+      <c r="B87" t="s">
+        <v>167</v>
+      </c>
+      <c r="C87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>150</v>
+      </c>
+      <c r="B88" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" t="s">
+        <v>173</v>
+      </c>
+      <c r="C90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>150</v>
+      </c>
+      <c r="B91" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>177</v>
+      </c>
+      <c r="B92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" t="s">
+        <v>182</v>
+      </c>
+      <c r="C94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>184</v>
+      </c>
+      <c r="B95" t="s">
+        <v>185</v>
+      </c>
+      <c r="C95" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97" t="s">
+        <v>190</v>
+      </c>
+      <c r="C97" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>187</v>
+      </c>
+      <c r="B98" t="s">
+        <v>192</v>
+      </c>
+      <c r="C98" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>187</v>
+      </c>
+      <c r="B99" t="s">
+        <v>194</v>
+      </c>
+      <c r="C99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>187</v>
+      </c>
+      <c r="B100" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>187</v>
+      </c>
+      <c r="B102" t="s">
+        <v>199</v>
+      </c>
+      <c r="C102" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>201</v>
+      </c>
+      <c r="C103" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>187</v>
+      </c>
+      <c r="B104" t="s">
+        <v>203</v>
+      </c>
+      <c r="C104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>187</v>
+      </c>
+      <c r="B105" t="s">
+        <v>205</v>
+      </c>
+      <c r="C105" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" t="s">
+        <v>207</v>
+      </c>
+      <c r="C106" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
+        <v>209</v>
+      </c>
+      <c r="C107" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>187</v>
+      </c>
+      <c r="B108" t="s">
+        <v>211</v>
+      </c>
+      <c r="C108" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" t="s">
+        <v>213</v>
+      </c>
+      <c r="C109" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>187</v>
+      </c>
+      <c r="B110" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>187</v>
+      </c>
+      <c r="B111" t="s">
+        <v>216</v>
+      </c>
+      <c r="C111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>218</v>
+      </c>
+      <c r="B112" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>218</v>
+      </c>
+      <c r="B113" t="s">
+        <v>66</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>220</v>
+      </c>
+      <c r="B114" t="s">
+        <v>221</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>222</v>
+      </c>
+      <c r="B115" t="s">
+        <v>223</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>224</v>
+      </c>
+      <c r="B116" t="s">
+        <v>225</v>
+      </c>
+      <c r="C116" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>224</v>
+      </c>
+      <c r="B117" t="s">
+        <v>227</v>
+      </c>
+      <c r="C117" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>224</v>
+      </c>
+      <c r="B118" t="s">
+        <v>229</v>
+      </c>
+      <c r="C118" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>224</v>
+      </c>
+      <c r="B119" t="s">
+        <v>231</v>
+      </c>
+      <c r="C119" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>224</v>
+      </c>
+      <c r="B120" t="s">
+        <v>233</v>
+      </c>
+      <c r="C120" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>224</v>
+      </c>
+      <c r="B121" t="s">
+        <v>235</v>
+      </c>
+      <c r="C121" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>224</v>
+      </c>
+      <c r="B122" t="s">
+        <v>237</v>
+      </c>
+      <c r="C122" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" t="s">
+        <v>240</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>241</v>
+      </c>
+      <c r="B124" t="s">
+        <v>242</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>243</v>
+      </c>
+      <c r="B125" t="s">
+        <v>244</v>
+      </c>
+      <c r="C125" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>246</v>
+      </c>
+      <c r="B126" t="s">
+        <v>66</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>246</v>
+      </c>
+      <c r="B127" t="s">
+        <v>247</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>248</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>249</v>
+      </c>
+      <c r="B129" t="s">
+        <v>250</v>
+      </c>
+      <c r="C129" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>249</v>
+      </c>
+      <c r="B130" t="s">
+        <v>252</v>
+      </c>
+      <c r="C130" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>249</v>
+      </c>
+      <c r="B131" t="s">
+        <v>254</v>
+      </c>
+      <c r="C131" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>249</v>
+      </c>
+      <c r="B132" t="s">
+        <v>256</v>
+      </c>
+      <c r="C132" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>249</v>
+      </c>
+      <c r="B133" t="s">
+        <v>258</v>
+      </c>
+      <c r="C133" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>249</v>
+      </c>
+      <c r="B134" t="s">
+        <v>260</v>
+      </c>
+      <c r="C134" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>249</v>
+      </c>
+      <c r="B135" t="s">
+        <v>262</v>
+      </c>
+      <c r="C135" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>249</v>
+      </c>
+      <c r="B136" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>266</v>
+      </c>
+      <c r="B137" t="s">
+        <v>267</v>
+      </c>
+      <c r="C137" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>266</v>
+      </c>
+      <c r="B138" t="s">
+        <v>269</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>270</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>271</v>
+      </c>
+      <c r="B140" t="s">
+        <v>250</v>
+      </c>
+      <c r="C140" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>271</v>
+      </c>
+      <c r="B141" t="s">
+        <v>252</v>
+      </c>
+      <c r="C141" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>271</v>
+      </c>
+      <c r="B142" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>271</v>
+      </c>
+      <c r="B143" t="s">
+        <v>254</v>
+      </c>
+      <c r="C143" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>271</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>271</v>
+      </c>
+      <c r="B145" t="s">
+        <v>18</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>271</v>
+      </c>
+      <c r="B146" t="s">
+        <v>256</v>
+      </c>
+      <c r="C146" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>271</v>
+      </c>
+      <c r="B147" t="s">
+        <v>260</v>
+      </c>
+      <c r="C147" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>271</v>
+      </c>
+      <c r="B148" t="s">
+        <v>29</v>
+      </c>
+      <c r="C148" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>271</v>
+      </c>
+      <c r="B149" t="s">
+        <v>33</v>
+      </c>
+      <c r="C149" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>271</v>
+      </c>
+      <c r="B150" t="s">
+        <v>262</v>
+      </c>
+      <c r="C150" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>275</v>
+      </c>
+      <c r="B151" t="s">
+        <v>276</v>
+      </c>
+      <c r="C151" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>275</v>
+      </c>
+      <c r="B152" t="s">
+        <v>278</v>
+      </c>
+      <c r="C152" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>275</v>
+      </c>
+      <c r="B153" t="s">
+        <v>280</v>
+      </c>
+      <c r="C153" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>275</v>
+      </c>
+      <c r="B154" t="s">
+        <v>282</v>
+      </c>
+      <c r="C154" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>275</v>
+      </c>
+      <c r="B155" t="s">
+        <v>284</v>
+      </c>
+      <c r="C155" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>275</v>
+      </c>
+      <c r="B156" t="s">
+        <v>286</v>
+      </c>
+      <c r="C156" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>288</v>
+      </c>
+      <c r="B157" t="s">
+        <v>289</v>
+      </c>
+      <c r="C157" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>288</v>
+      </c>
+      <c r="B158" t="s">
+        <v>291</v>
+      </c>
+      <c r="C158" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>288</v>
+      </c>
+      <c r="B159" t="s">
+        <v>293</v>
+      </c>
+      <c r="C159" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>288</v>
+      </c>
+      <c r="B160" t="s">
+        <v>295</v>
+      </c>
+      <c r="C160" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>288</v>
+      </c>
+      <c r="B161" t="s">
+        <v>297</v>
+      </c>
+      <c r="C161" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>288</v>
+      </c>
+      <c r="B162" t="s">
+        <v>299</v>
+      </c>
+      <c r="C162" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>288</v>
+      </c>
+      <c r="B163" t="s">
+        <v>300</v>
+      </c>
+      <c r="C163" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>288</v>
+      </c>
+      <c r="B164" t="s">
+        <v>302</v>
+      </c>
+      <c r="C164" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>304</v>
+      </c>
+      <c r="B165" t="s">
+        <v>305</v>
+      </c>
+      <c r="C165" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>304</v>
+      </c>
+      <c r="B166" t="s">
+        <v>307</v>
+      </c>
+      <c r="C166" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>304</v>
+      </c>
+      <c r="B167" t="s">
+        <v>244</v>
+      </c>
+      <c r="C167" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>304</v>
+      </c>
+      <c r="B168" t="s">
+        <v>310</v>
+      </c>
+      <c r="C168" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>304</v>
+      </c>
+      <c r="B169" t="s">
+        <v>53</v>
+      </c>
+      <c r="C169" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>304</v>
+      </c>
+      <c r="B170" t="s">
+        <v>313</v>
+      </c>
+      <c r="C170" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>304</v>
+      </c>
+      <c r="B171" t="s">
+        <v>62</v>
+      </c>
+      <c r="C171" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>304</v>
+      </c>
+      <c r="B172" t="s">
+        <v>316</v>
+      </c>
+      <c r="C172" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>318</v>
+      </c>
+      <c r="B173" t="s">
+        <v>305</v>
+      </c>
+      <c r="C173" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>318</v>
+      </c>
+      <c r="B174" t="s">
+        <v>307</v>
+      </c>
+      <c r="C174" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>318</v>
+      </c>
+      <c r="B175" t="s">
+        <v>321</v>
+      </c>
+      <c r="C175" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>318</v>
+      </c>
+      <c r="B176" t="s">
+        <v>244</v>
+      </c>
+      <c r="C176" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>318</v>
+      </c>
+      <c r="B177" t="s">
+        <v>310</v>
+      </c>
+      <c r="C177" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A178" t="s">
+        <v>318</v>
+      </c>
+      <c r="B178" t="s">
+        <v>325</v>
+      </c>
+      <c r="C178" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>318</v>
+      </c>
+      <c r="B179" t="s">
+        <v>313</v>
+      </c>
+      <c r="C179" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>318</v>
+      </c>
+      <c r="B180" t="s">
+        <v>316</v>
+      </c>
+      <c r="C180" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>328</v>
+      </c>
+      <c r="B181" t="s">
+        <v>293</v>
+      </c>
+      <c r="C181" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>329</v>
+      </c>
+      <c r="B182" t="s">
+        <v>330</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>331</v>
+      </c>
+      <c r="B183" t="s">
+        <v>205</v>
+      </c>
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>332</v>
+      </c>
+      <c r="B184" t="s">
+        <v>333</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>334</v>
+      </c>
+      <c r="B185" t="s">
+        <v>335</v>
+      </c>
+      <c r="C185" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A186" t="s">
+        <v>334</v>
+      </c>
+      <c r="B186" t="s">
+        <v>337</v>
+      </c>
+      <c r="C186" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>334</v>
+      </c>
+      <c r="B187" t="s">
+        <v>231</v>
+      </c>
+      <c r="C187" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A188" t="s">
+        <v>334</v>
+      </c>
+      <c r="B188" t="s">
+        <v>235</v>
+      </c>
+      <c r="C188" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A189" t="s">
+        <v>334</v>
+      </c>
+      <c r="B189" t="s">
+        <v>341</v>
+      </c>
+      <c r="C189" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A190" t="s">
+        <v>343</v>
+      </c>
+      <c r="B190" t="s">
+        <v>84</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A191" t="s">
+        <v>344</v>
+      </c>
+      <c r="B191" t="s">
+        <v>345</v>
+      </c>
+      <c r="C191" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A192" t="s">
+        <v>344</v>
+      </c>
+      <c r="B192" t="s">
+        <v>66</v>
+      </c>
+      <c r="C192" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A193" t="s">
+        <v>346</v>
+      </c>
+      <c r="B193" t="s">
+        <v>347</v>
+      </c>
+      <c r="C193" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A194" t="s">
+        <v>346</v>
+      </c>
+      <c r="B194" t="s">
+        <v>349</v>
+      </c>
+      <c r="C194" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A195" t="s">
+        <v>351</v>
+      </c>
+      <c r="B195" t="s">
+        <v>352</v>
+      </c>
+      <c r="C195" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>351</v>
+      </c>
+      <c r="B196" t="s">
+        <v>354</v>
+      </c>
+      <c r="C196" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>351</v>
+      </c>
+      <c r="B197" t="s">
+        <v>356</v>
+      </c>
+      <c r="C197" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A198" t="s">
+        <v>351</v>
+      </c>
+      <c r="B198" t="s">
+        <v>66</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A199" t="s">
+        <v>358</v>
+      </c>
+      <c r="B199" t="s">
+        <v>359</v>
+      </c>
+      <c r="C199" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>358</v>
+      </c>
+      <c r="B200" t="s">
+        <v>203</v>
+      </c>
+      <c r="C200" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A201" t="s">
+        <v>358</v>
+      </c>
+      <c r="B201" t="s">
+        <v>214</v>
+      </c>
+      <c r="C201" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A202" t="s">
+        <v>362</v>
+      </c>
+      <c r="B202" t="s">
+        <v>363</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>364</v>
+      </c>
+      <c r="B203" t="s">
+        <v>365</v>
+      </c>
+      <c r="C203" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>364</v>
+      </c>
+      <c r="B204" t="s">
+        <v>367</v>
+      </c>
+      <c r="C204" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>364</v>
+      </c>
+      <c r="B205" t="s">
+        <v>369</v>
+      </c>
+      <c r="C205" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>364</v>
+      </c>
+      <c r="B206" t="s">
+        <v>371</v>
+      </c>
+      <c r="C206" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>364</v>
+      </c>
+      <c r="B207" t="s">
+        <v>373</v>
+      </c>
+      <c r="C207" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>364</v>
+      </c>
+      <c r="B208" t="s">
+        <v>375</v>
+      </c>
+      <c r="C208" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>364</v>
+      </c>
+      <c r="B209" t="s">
+        <v>377</v>
+      </c>
+      <c r="C209" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>364</v>
+      </c>
+      <c r="B210" t="s">
+        <v>379</v>
+      </c>
+      <c r="C210" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>364</v>
+      </c>
+      <c r="B211" t="s">
+        <v>381</v>
+      </c>
+      <c r="C211" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>364</v>
+      </c>
+      <c r="B212" t="s">
+        <v>383</v>
+      </c>
+      <c r="C212" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>385</v>
+      </c>
+      <c r="B213" t="s">
+        <v>386</v>
+      </c>
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>387</v>
+      </c>
+      <c r="B214" t="s">
+        <v>388</v>
+      </c>
+      <c r="C214" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>387</v>
+      </c>
+      <c r="B215" t="s">
+        <v>390</v>
+      </c>
+      <c r="C215" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>392</v>
+      </c>
+      <c r="B216" t="s">
+        <v>393</v>
+      </c>
+      <c r="C216" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>392</v>
+      </c>
+      <c r="B217" t="s">
+        <v>395</v>
+      </c>
+      <c r="C217" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>392</v>
+      </c>
+      <c r="B218" t="s">
+        <v>397</v>
+      </c>
+      <c r="C218" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>392</v>
+      </c>
+      <c r="B219" t="s">
+        <v>399</v>
+      </c>
+      <c r="C219" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>392</v>
+      </c>
+      <c r="B220" t="s">
+        <v>401</v>
+      </c>
+      <c r="C220" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>392</v>
+      </c>
+      <c r="B221" t="s">
+        <v>403</v>
+      </c>
+      <c r="C221" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>392</v>
+      </c>
+      <c r="B222" t="s">
+        <v>405</v>
+      </c>
+      <c r="C222" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>392</v>
+      </c>
+      <c r="B223" t="s">
+        <v>407</v>
+      </c>
+      <c r="C223" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>392</v>
+      </c>
+      <c r="B224" t="s">
+        <v>409</v>
+      </c>
+      <c r="C224" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>392</v>
+      </c>
+      <c r="B225" t="s">
+        <v>411</v>
+      </c>
+      <c r="C225" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>392</v>
+      </c>
+      <c r="B226" t="s">
+        <v>413</v>
+      </c>
+      <c r="C226" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>392</v>
+      </c>
+      <c r="B227" t="s">
+        <v>142</v>
+      </c>
+      <c r="C227" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A228" t="s">
+        <v>392</v>
+      </c>
+      <c r="B228" t="s">
+        <v>416</v>
+      </c>
+      <c r="C228" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>392</v>
+      </c>
+      <c r="B229" t="s">
+        <v>418</v>
+      </c>
+      <c r="C229" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>392</v>
+      </c>
+      <c r="B230" t="s">
+        <v>420</v>
+      </c>
+      <c r="C230" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>392</v>
+      </c>
+      <c r="B231" t="s">
+        <v>422</v>
+      </c>
+      <c r="C231" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>392</v>
+      </c>
+      <c r="B232" t="s">
+        <v>424</v>
+      </c>
+      <c r="C232" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>426</v>
+      </c>
+      <c r="B233" t="s">
+        <v>91</v>
+      </c>
+      <c r="C233" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>426</v>
+      </c>
+      <c r="B234" t="s">
+        <v>93</v>
+      </c>
+      <c r="C234" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>426</v>
+      </c>
+      <c r="B235" t="s">
+        <v>95</v>
+      </c>
+      <c r="C235" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>427</v>
+      </c>
+      <c r="B236" t="s">
+        <v>428</v>
+      </c>
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
+        <v>429</v>
+      </c>
+      <c r="B237" t="s">
+        <v>430</v>
+      </c>
+      <c r="C237" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>432</v>
+      </c>
+      <c r="B238" t="s">
+        <v>433</v>
+      </c>
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A239" t="s">
+        <v>434</v>
+      </c>
+      <c r="B239" t="s">
+        <v>435</v>
+      </c>
+      <c r="C239" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>434</v>
+      </c>
+      <c r="B240" t="s">
+        <v>437</v>
+      </c>
+      <c r="C240" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A241" t="s">
+        <v>439</v>
+      </c>
+      <c r="B241" t="s">
+        <v>440</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A242" t="s">
+        <v>441</v>
+      </c>
+      <c r="B242" t="s">
+        <v>442</v>
+      </c>
+      <c r="C242" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>443</v>
+      </c>
+      <c r="B243" t="s">
+        <v>444</v>
+      </c>
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A244" t="s">
+        <v>445</v>
+      </c>
+      <c r="B244" t="s">
+        <v>446</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A245" t="s">
+        <v>447</v>
+      </c>
+      <c r="B245" t="s">
+        <v>448</v>
+      </c>
+      <c r="C245" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A246" t="s">
+        <v>450</v>
+      </c>
+      <c r="B246" t="s">
+        <v>451</v>
+      </c>
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A247" t="s">
+        <v>452</v>
+      </c>
+      <c r="B247" t="s">
+        <v>453</v>
+      </c>
+      <c r="C247" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A248" t="s">
+        <v>452</v>
+      </c>
+      <c r="B248" t="s">
+        <v>455</v>
+      </c>
+      <c r="C248" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>452</v>
+      </c>
+      <c r="B249" t="s">
+        <v>457</v>
+      </c>
+      <c r="C249" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>459</v>
+      </c>
+      <c r="B250" t="s">
+        <v>460</v>
+      </c>
+      <c r="C250" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>461</v>
+      </c>
+      <c r="B251" t="s">
+        <v>462</v>
+      </c>
+      <c r="C251" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>461</v>
+      </c>
+      <c r="B252" t="s">
+        <v>464</v>
+      </c>
+      <c r="C252" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>466</v>
+      </c>
+      <c r="B253" t="s">
+        <v>467</v>
+      </c>
+      <c r="C253" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>466</v>
+      </c>
+      <c r="B254" t="s">
+        <v>469</v>
+      </c>
+      <c r="C254" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>466</v>
+      </c>
+      <c r="B255" t="s">
+        <v>471</v>
+      </c>
+      <c r="C255" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>473</v>
+      </c>
+      <c r="B256" t="s">
+        <v>474</v>
+      </c>
+      <c r="C256" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A257" t="s">
+        <v>473</v>
+      </c>
+      <c r="B257" t="s">
+        <v>476</v>
+      </c>
+      <c r="C257" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>473</v>
+      </c>
+      <c r="B258" t="s">
+        <v>478</v>
+      </c>
+      <c r="C258" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A259" t="s">
+        <v>473</v>
+      </c>
+      <c r="B259" t="s">
+        <v>418</v>
+      </c>
+      <c r="C259" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A260" t="s">
+        <v>481</v>
+      </c>
+      <c r="B260" t="s">
+        <v>482</v>
+      </c>
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>483</v>
+      </c>
+      <c r="B261" t="s">
+        <v>484</v>
+      </c>
+      <c r="C261" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>485</v>
+      </c>
+      <c r="B262" t="s">
+        <v>12</v>
+      </c>
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A263" t="s">
+        <v>486</v>
+      </c>
+      <c r="B263" t="s">
+        <v>250</v>
+      </c>
+      <c r="C263" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A264" t="s">
+        <v>486</v>
+      </c>
+      <c r="B264" t="s">
+        <v>252</v>
+      </c>
+      <c r="C264" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>486</v>
+      </c>
+      <c r="B265" t="s">
+        <v>254</v>
+      </c>
+      <c r="C265" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A266" t="s">
+        <v>486</v>
+      </c>
+      <c r="B266" t="s">
+        <v>256</v>
+      </c>
+      <c r="C266" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>486</v>
+      </c>
+      <c r="B267" t="s">
+        <v>260</v>
+      </c>
+      <c r="C267" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A268" t="s">
+        <v>486</v>
+      </c>
+      <c r="B268" t="s">
+        <v>262</v>
+      </c>
+      <c r="C268" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>487</v>
+      </c>
+      <c r="B269" t="s">
+        <v>488</v>
+      </c>
+      <c r="C269" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A270" t="s">
+        <v>487</v>
+      </c>
+      <c r="B270" t="s">
+        <v>490</v>
+      </c>
+      <c r="C270" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A271" t="s">
+        <v>487</v>
+      </c>
+      <c r="B271" t="s">
+        <v>492</v>
+      </c>
+      <c r="C271" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A272" t="s">
+        <v>487</v>
+      </c>
+      <c r="B272" t="s">
+        <v>494</v>
+      </c>
+      <c r="C272" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A273" t="s">
+        <v>487</v>
+      </c>
+      <c r="B273" t="s">
+        <v>496</v>
+      </c>
+      <c r="C273" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A274" t="s">
+        <v>487</v>
+      </c>
+      <c r="B274" t="s">
+        <v>498</v>
+      </c>
+      <c r="C274" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A275" t="s">
+        <v>487</v>
+      </c>
+      <c r="B275" t="s">
+        <v>500</v>
+      </c>
+      <c r="C275" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A276" t="s">
+        <v>487</v>
+      </c>
+      <c r="B276" t="s">
+        <v>502</v>
+      </c>
+      <c r="C276" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A277" t="s">
+        <v>487</v>
+      </c>
+      <c r="B277" t="s">
+        <v>504</v>
+      </c>
+      <c r="C277" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A278" t="s">
+        <v>506</v>
+      </c>
+      <c r="B278" t="s">
+        <v>507</v>
+      </c>
+      <c r="C278" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A279" t="s">
+        <v>509</v>
+      </c>
+      <c r="B279" t="s">
+        <v>510</v>
+      </c>
+      <c r="C279" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A280" t="s">
+        <v>509</v>
+      </c>
+      <c r="B280" t="s">
+        <v>512</v>
+      </c>
+      <c r="C280" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A281" t="s">
+        <v>509</v>
+      </c>
+      <c r="B281" t="s">
+        <v>514</v>
+      </c>
+      <c r="C281" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A282" t="s">
+        <v>509</v>
+      </c>
+      <c r="B282" t="s">
+        <v>516</v>
+      </c>
+      <c r="C282" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A283" t="s">
+        <v>518</v>
+      </c>
+      <c r="B283" t="s">
+        <v>519</v>
+      </c>
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42819821-0C53-4A2C-8873-DB33CC2A5C79}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
